--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/flattened_e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/flattened_e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P006_2024年度资本管理第三支柱信息披露报告" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P006_2024年度资本管理第三支柱信息披露报告" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P009_风险加权资产概况" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,11 +488,2894 @@
           <t>备注特征</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>记录1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>调整后表内外资产余额</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>42755544</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>记录2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>调整后表内外资产余额</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>42815730</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>记录3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>调整后表内外资产余额</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>42314726</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>记录4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>调整后表内外资产余额</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>41837451</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>记录5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>杠杆率(%)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7.78</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>记录6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>杠杆率(%)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>记录7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>杠杆率(%)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>记录8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>杠杆率(%)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>记录9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>杠杆率a(%)1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7.78</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>记录10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>杠杆率a(%)1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>记录11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>杠杆率a(%)1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>记录12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>杠杆率a(%)1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>记录13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>杠杆率b(%)2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>记录14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>杠杆率b(%)2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>记录15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>杠杆率b(%)2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>记录16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>杠杆率b(%)2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>记录17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>杠杆率c(%)3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>记录18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>杠杆率c(%)3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>记录19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>杠杆率c(%)3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>记录20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>杠杆率c(%)3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>记录21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6237408</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>记录22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6148940</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>记录23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6115852</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>记录24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6059382</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>记录25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>4957733</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>记录26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5119129</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>记录27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>4877791</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>记录28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>4510003</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>记录29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>流动性覆盖率(%)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>125.73</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>记录30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>流动性覆盖率(%)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>120.29</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>记录31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>流动性覆盖率(%)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>125.43</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>记录32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>流动性覆盖率(%)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>134.46</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>记录33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>可用稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>28158322</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>记录34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>可用稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>28350638</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>记录35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>可用稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>28236945</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>记录36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>可用稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>28350972</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>记录37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>所需稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>21027700</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>记录38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>所需稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>20928125</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>记录39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>所需稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>20917739</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>记录40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>所需稳定资金合计</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>22174688</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>记录41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>净稳定资金比例(%)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;12月31日</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>133.91</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>记录42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>净稳定资金比例(%)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;9月30日</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>135.47</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>记录43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>净稳定资金比例(%)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;6月30日</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>134.99</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>记录44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>净稳定资金比例(%)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2024年&gt;&gt;3月31日</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>127.85</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>字段名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>银行名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>表名</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>页号</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>主体</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>纵向层级路径</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>横向层级路径</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>数据类型</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>币种</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>报告期</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>行标记</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>备注特征</t>
+        </is>
+      </c>
       <c r="O1" t="inlineStr"/>
       <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -506,12 +3390,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,17 +3405,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>调整后表内外资产余额</t>
+          <t>信用风险</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,30 +3425,25 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31 日</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>42755544</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>19814943</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,12 +3458,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -594,17 +3473,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>调整后表内外资产余额</t>
+          <t>信用风险</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -614,30 +3493,25 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>42815730</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>20185885</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -652,12 +3526,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -667,17 +3541,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>调整后表内外资产余额</t>
+          <t>信用风险</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -687,30 +3561,25 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>42314726</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>1585195</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -725,12 +3594,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -740,17 +3609,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>调整后表内外资产余额</t>
+          <t>信用风险（不包括交易对手信用风险、信用估值调整风险、银行账簿资产管理产品和银行账簿资产证券化）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -760,30 +3629,25 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>41837451</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>19433391</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -798,12 +3662,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,17 +3677,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>杠杆率(%)</t>
+          <t>信用风险（不包括交易对手信用风险、信用估值调整风险、银行账簿资产管理产品和银行账簿资产证券化）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -833,30 +3697,25 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>7.78</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>19818263</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -871,12 +3730,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -886,17 +3745,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>杠杆率(%)</t>
+          <t>信用风险（不包括交易对手信用风险、信用估值调整风险、银行账簿资产管理产品和银行账簿资产证券化）</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -906,30 +3765,25 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>1554670</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -944,12 +3798,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -959,17 +3813,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>杠杆率(%)</t>
+          <t>其中:权重法</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -979,30 +3833,25 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>5820738</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1017,12 +3866,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1032,17 +3881,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>杠杆率(%)</t>
+          <t>其中:权重法</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1052,30 +3901,25 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>5596995</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1090,12 +3934,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1105,17 +3949,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>杠杆率a(%)1</t>
+          <t>其中:权重法</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1125,30 +3969,25 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7.78</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>465658</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1163,12 +4002,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1178,12 +4017,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>杠杆率a(%)1</t>
+          <t>其中:证券、商品、外汇交易清算过程中形成的风险暴露</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1198,30 +4037,25 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1236,12 +4070,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1251,12 +4085,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>杠杆率a(%)1</t>
+          <t>其中:证券、商品、外汇交易清算过程中形成的风险暴露</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1271,30 +4105,25 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1309,12 +4138,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1324,12 +4153,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>杠杆率a(%)1</t>
+          <t>其中:证券、商品、外汇交易清算过程中形成的风险暴露</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1344,30 +4173,25 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1382,12 +4206,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1397,17 +4221,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>杠杆率b(%)2</t>
+          <t>其中:门槛扣除项中未扣除部分</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1417,30 +4241,25 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>363177</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1455,12 +4274,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1470,17 +4289,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>杠杆率b(%)2</t>
+          <t>其中:门槛扣除项中未扣除部分</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1490,30 +4309,25 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7.75</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>369459</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1528,12 +4342,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1543,17 +4357,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>杠杆率b(%)2</t>
+          <t>其中:门槛扣除项中未扣除部分</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1563,30 +4377,25 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>29054</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1601,12 +4410,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1616,17 +4425,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>杠杆率b(%)2</t>
+          <t>其中:初级内部评级法</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1636,30 +4445,25 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>11323706</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1674,12 +4478,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1689,12 +4493,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>合格优质流动性资产</t>
+          <t>其中:初级内部评级法</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1707,28 +4511,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6237408</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>11946337</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1743,12 +4546,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1758,12 +4561,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>合格优质流动性资产</t>
+          <t>其中:初级内部评级法</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1776,28 +4579,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6148940</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>905896</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1812,12 +4614,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1827,12 +4629,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>合格优质流动性资产</t>
+          <t>其中:高级内部评级法</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1845,28 +4647,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6115852</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>2288947</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1881,12 +4682,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1896,12 +4697,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>合格优质流动性资产</t>
+          <t>其中:高级内部评级法</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1914,28 +4715,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6059382</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>2274931</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1950,12 +4750,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1965,12 +4765,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>现金净流出量</t>
+          <t>其中:高级内部评级法</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1983,28 +4783,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4957733</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>183116</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2019,12 +4818,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2034,12 +4833,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>现金净流出量</t>
+          <t>交易对手信用风险</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2052,28 +4851,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5119129</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>117100</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2088,12 +4886,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2103,12 +4901,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>现金净流出量</t>
+          <t>交易对手信用风险</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2121,28 +4919,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4877791</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>115575</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2157,12 +4954,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2172,12 +4969,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>现金净流出量</t>
+          <t>交易对手信用风险</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2190,28 +4987,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4510003</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>9368</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2226,12 +5022,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2241,17 +5037,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>可用稳定资金合计</t>
+          <t>其中:标准法</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2259,28 +5055,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>28158322</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>117100</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2295,12 +5090,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2310,17 +5105,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>可用稳定资金合计</t>
+          <t>其中:标准法</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2328,28 +5123,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>28350638</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>115575</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2364,12 +5158,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2379,17 +5173,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>可用稳定资金合计</t>
+          <t>其中:标准法</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2397,28 +5191,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28236945</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>9368</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2433,12 +5226,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2448,17 +5241,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>可用稳定资金合计</t>
+          <t>信用估值调整风险</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2466,28 +5259,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28350972</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>46944</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2502,12 +5294,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2517,17 +5309,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>所需稳定资金合计</t>
+          <t>信用估值调整风险</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2535,28 +5327,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21027700</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>36447</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2571,12 +5362,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2586,17 +5377,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>所需稳定资金合计</t>
+          <t>信用估值调整风险</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2604,28 +5395,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20928125</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>3756</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2640,12 +5430,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2655,17 +5445,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>所需稳定资金合计</t>
+          <t>银行账簿资产管理产品</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2673,28 +5463,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20917739</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>199861</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2709,12 +5498,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2724,17 +5513,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>所需稳定资金合计</t>
+          <t>银行账簿资产管理产品</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>余额</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2742,28 +5531,27 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>22174688</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>197318</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2778,12 +5566,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2793,17 +5581,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>净稳定资金比例(%)</t>
+          <t>银行账簿资产管理产品</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2813,30 +5601,25 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>133.91</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>15989</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2851,12 +5634,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2866,17 +5649,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>净稳定资金比例(%)</t>
+          <t>其中:穿透法</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2886,30 +5669,25 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>135.47</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2924,12 +5702,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2939,17 +5717,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>净稳定资金比例(%)</t>
+          <t>其中:穿透法</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2959,30 +5737,25 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年9月30日</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>134.99</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2997,12 +5770,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P006_2024年度资本管理第三支柱信息披露报告</t>
+          <t>P009_风险加权资产概况</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3012,17 +5785,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>净稳定资金比例(%)</t>
+          <t>其中:穿透法</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;3月31日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>占比</t>
+          <t>发生额</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3032,219 +5805,2241 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>元</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年12月31日</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>127.85</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>记录37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>其中:授权基础法</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>192913</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>记录38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>其中:授权基础法</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>195293</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>记录39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>其中:授权基础法</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15433</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>记录40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>其中:适用1250%风险权重</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>记录41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>其中:适用1250%风险权重</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>记录42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>其中:适用1250%风险权重</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>记录43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>银行账簿资产证券化1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>17647</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>记录44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>银行账簿资产证券化1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>18282</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>记录45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>银行账簿资产证券化1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>记录46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>其中:资产证券化外部评级法</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>记录47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>其中:资产证券化外部评级法</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>记录48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>其中:资产证券化外部评级法</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>记录49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>其中:资产证券化标准法</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>7818</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>记录50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>其中:资产证券化标准法</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>7813</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>记录51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>其中:资产证券化标准法</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>记录52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>市场风险</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>250577</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>记录53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>市场风险</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>194481</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>记录54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>市场风险</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>20046</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>记录55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>其中:标准法</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>250577</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>记录56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>其中:标准法</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>194481</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>记录57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>其中:标准法</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>20046</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>记录58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>交易账簿和银行账簿间转换的资本要求</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>44651</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>记录59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>交易账簿和银行账簿间转换的资本要求</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>记录60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>交易账簿和银行账簿间转换的资本要求</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>记录61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>操作风险</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1744419</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>记录62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>操作风险</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1770189</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>记录63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>操作风险</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>139554</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>记录64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>因应用资本底线而导致的额外调整</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>记录65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>因应用资本底线而导致的额外调整</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>记录66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>21854590</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>记录67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>P009_风险加权资产概况</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>余额</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2024年9月30日</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>221505551748367</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
